--- a/tests/outputs/reader.xlsx
+++ b/tests/outputs/reader.xlsx
@@ -164,7 +164,7 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>offer_id</t>
+        <t>Offer</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
